--- a/runs/KO/2026-10-13/bear/scratch/c1_margin_319/dcf.xlsx
+++ b/runs/KO/2026-10-13/bear/scratch/c1_margin_319/dcf.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.04686038779956427</v>
+        <v>0.04686038779956428</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0.03</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>52862.02214222582</v>
+        <v>52363.32382012936</v>
       </c>
     </row>
     <row r="4">
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>16862.98506337004</v>
+        <v>16703.90029862127</v>
       </c>
     </row>
     <row r="6">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12113.55357322642</v>
+        <v>11999.27476593183</v>
       </c>
     </row>
     <row r="12">
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8731.767680724755</v>
+        <v>8649.392513925466</v>
       </c>
     </row>
     <row r="16">
@@ -1419,7 +1419,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>47813.95117821754</v>
+        <v>47321.53673026581</v>
       </c>
     </row>
     <row r="21">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>12151.65440316515</v>
+        <v>12037.01615407869</v>
       </c>
     </row>
     <row r="22">
@@ -1447,7 +1447,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>219117.0516036344</v>
+        <v>217049.9096073738</v>
       </c>
     </row>
     <row r="23">
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>157945.327762208</v>
+        <v>156455.2775003005</v>
       </c>
     </row>
     <row r="24">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>205759.2789404255</v>
+        <v>203776.8142305663</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>206170.7789404255</v>
+        <v>204188.3142305663</v>
       </c>
     </row>
     <row r="27">
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>209403.3580630757</v>
+        <v>207301.0543333887</v>
       </c>
     </row>
     <row r="28">
@@ -1531,7 +1531,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>48.6758154493435</v>
+        <v>48.1871348985097</v>
       </c>
     </row>
     <row r="29">
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-0.4598777856</v>
+        <v>-0.4653003392</v>
       </c>
     </row>
   </sheetData>
